--- a/data/sample/table/anken.xlsx
+++ b/data/sample/table/anken.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\dev\shinsa\data\sample\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46830B32-7E42-44A3-947D-C80B57313044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F6BF5E-699E-4388-8CDA-A755B19942CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1872" yWindow="1872" windowWidth="13020" windowHeight="9180" xr2:uid="{5ACF79A2-5CCA-4A72-B36D-BEFD8CE971BC}"/>
+    <workbookView xWindow="11976" yWindow="300" windowWidth="13020" windowHeight="9180" xr2:uid="{5ACF79A2-5CCA-4A72-B36D-BEFD8CE971BC}"/>
   </bookViews>
   <sheets>
     <sheet name="anken" sheetId="1" r:id="rId1"/>
@@ -354,7 +354,7 @@
     <t>3,500,000</t>
   </si>
   <si>
-    <t>1</t>
+    <t>123456</t>
   </si>
   <si>
     <t>0.88</t>
